--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N42_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N42_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>7.709887658155151</v>
+        <v>1.252856744450212</v>
       </c>
       <c r="D2" t="n">
-        <v>6.366806878621965</v>
+        <v>1.034606117776069</v>
       </c>
       <c r="E2" t="n">
-        <v>23.47789588691396</v>
+        <v>3.815158081623518</v>
       </c>
       <c r="F2" t="n">
-        <v>18.73037678251953</v>
+        <v>3.043686227159424</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>1.727833980043553</v>
+        <v>0.2807730217570774</v>
       </c>
       <c r="D3" t="n">
-        <v>53.14999874089875</v>
+        <v>8.636874795396047</v>
       </c>
       <c r="E3" t="n">
-        <v>23.47789588691396</v>
+        <v>3.815158081623518</v>
       </c>
       <c r="F3" t="n">
-        <v>18.73037678251953</v>
+        <v>3.043686227159424</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>16.11876375012325</v>
+        <v>2.619299109395028</v>
       </c>
       <c r="D4" t="n">
-        <v>15.83636044718358</v>
+        <v>2.573408572667331</v>
       </c>
       <c r="E4" t="n">
-        <v>23.47789588691396</v>
+        <v>3.815158081623518</v>
       </c>
       <c r="F4" t="n">
-        <v>18.73037678251953</v>
+        <v>3.043686227159424</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>61.437827866836</v>
+        <v>9.983647028360849</v>
       </c>
       <c r="D5" t="n">
-        <v>40.59928215976746</v>
+        <v>6.597383350962213</v>
       </c>
       <c r="E5" t="n">
-        <v>23.47789588691396</v>
+        <v>3.815158081623518</v>
       </c>
       <c r="F5" t="n">
-        <v>18.73037678251953</v>
+        <v>3.043686227159424</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
